--- a/project.xlsx
+++ b/project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirapajaisean/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B67AFD6C-4C68-0245-A7F2-162AE67D1064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14690B1C-3A91-5245-8C7E-84366699443F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6340" yWindow="1560" windowWidth="20700" windowHeight="14520" xr2:uid="{C7BD4B05-5881-B742-B6C7-DB8654AD8B2F}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>การพักผ่อน</t>
   </si>
   <si>
-    <t>ค่า BMI (เกณฑ์เอเชีย)</t>
-  </si>
-  <si>
     <t>คำแนะนำการออกกำลังกายจาก AI</t>
   </si>
   <si>
@@ -1154,6 +1151,9 @@
       </rPr>
       <t> แนะนำแอโรบิกในน้ำ หรือว่ายน้ำเต็มที่ 45-60 นาที เบิร์นไขมันได้ดีเยี่ยม</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ค่า BMI </t>
   </si>
 </sst>
 </file>
@@ -1541,10 +1541,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1552,16 +1552,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1569,16 +1569,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1586,16 +1586,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1603,16 +1603,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1620,16 +1620,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1637,16 +1637,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1654,16 +1654,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1671,16 +1671,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1688,16 +1688,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1705,16 +1705,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1722,16 +1722,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1739,16 +1739,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1756,16 +1756,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1773,16 +1773,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1790,16 +1790,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1807,16 +1807,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1824,16 +1824,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1841,16 +1841,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1858,16 +1858,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1875,16 +1875,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1892,16 +1892,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1909,16 +1909,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1926,16 +1926,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1943,16 +1943,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1960,16 +1960,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1977,16 +1977,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1994,16 +1994,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2011,16 +2011,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2028,16 +2028,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2045,16 +2045,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2062,16 +2062,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2079,16 +2079,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2096,16 +2096,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2113,16 +2113,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2130,16 +2130,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2147,16 +2147,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2164,16 +2164,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2181,16 +2181,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2198,16 +2198,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2215,16 +2215,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2232,16 +2232,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2249,16 +2249,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2266,16 +2266,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2283,16 +2283,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2300,16 +2300,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/project.xlsx
+++ b/project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirapajaisean/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14690B1C-3A91-5245-8C7E-84366699443F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EE4BEF-5CC7-884D-98EA-A0D3C1E0F2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6340" yWindow="1560" windowWidth="20700" windowHeight="14520" xr2:uid="{C7BD4B05-5881-B742-B6C7-DB8654AD8B2F}"/>
+    <workbookView xWindow="5820" yWindow="3060" windowWidth="28800" windowHeight="16080" xr2:uid="{C7BD4B05-5881-B742-B6C7-DB8654AD8B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1153,7 +1153,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ค่า BMI </t>
+    <t>ค่า BMI</t>
   </si>
 </sst>
 </file>

--- a/project.xlsx
+++ b/project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirapajaisean/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EE4BEF-5CC7-884D-98EA-A0D3C1E0F2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D130CC5-9AFF-4749-B7E4-AF1270BF83E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="3060" windowWidth="28800" windowHeight="16080" xr2:uid="{C7BD4B05-5881-B742-B6C7-DB8654AD8B2F}"/>
+    <workbookView xWindow="5720" yWindow="1840" windowWidth="28800" windowHeight="16080" xr2:uid="{C7BD4B05-5881-B742-B6C7-DB8654AD8B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>น้อย</t>
   </si>
   <si>
-    <t>ผอม (&lt; 18.5)</t>
-  </si>
-  <si>
     <r>
       <t>🛑 </t>
     </r>
@@ -82,9 +79,6 @@
     </r>
   </si>
   <si>
-    <t>ปกติ (18.5 - 22.9)</t>
-  </si>
-  <si>
     <r>
       <t>🛑 </t>
     </r>
@@ -109,9 +103,6 @@
     </r>
   </si>
   <si>
-    <t>ท้วม (23.0 - 24.9)</t>
-  </si>
-  <si>
     <r>
       <t>🛑 </t>
     </r>
@@ -136,9 +127,6 @@
     </r>
   </si>
   <si>
-    <t>อ้วน 1 (25.0 - 29.9)</t>
-  </si>
-  <si>
     <r>
       <t>🛑 </t>
     </r>
@@ -163,9 +151,6 @@
     </r>
   </si>
   <si>
-    <t>อ้วน 2 (30.0+)</t>
-  </si>
-  <si>
     <r>
       <t>🛑 </t>
     </r>
@@ -1154,13 +1139,28 @@
   </si>
   <si>
     <t>ค่า BMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ผอม </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ปกติ </t>
+  </si>
+  <si>
+    <t>ท้วม</t>
+  </si>
+  <si>
+    <t>อ้วน 1</t>
+  </si>
+  <si>
+    <t>อ้วน 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1181,6 +1181,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1541,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1558,10 +1565,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1575,10 +1582,10 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1592,10 +1599,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1609,10 +1616,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1626,10 +1633,10 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1640,13 +1647,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1657,13 +1664,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1674,13 +1681,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1691,13 +1698,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1708,13 +1715,13 @@
         <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1728,10 +1735,10 @@
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1745,10 +1752,10 @@
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1762,10 +1769,10 @@
         <v>4</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1779,10 +1786,10 @@
         <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1796,10 +1803,10 @@
         <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1807,16 +1814,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1824,16 +1831,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1841,16 +1848,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1858,16 +1865,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1875,16 +1882,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1892,16 +1899,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1909,16 +1916,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1926,16 +1933,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1943,16 +1950,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1960,16 +1967,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1977,16 +1984,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1994,16 +2001,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2011,16 +2018,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2028,16 +2035,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2045,16 +2052,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2068,10 +2075,10 @@
         <v>5</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2085,10 +2092,10 @@
         <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2102,10 +2109,10 @@
         <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2119,10 +2126,10 @@
         <v>5</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2136,10 +2143,10 @@
         <v>5</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2150,13 +2157,13 @@
         <v>5</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2167,13 +2174,13 @@
         <v>5</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2184,13 +2191,13 @@
         <v>5</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2201,13 +2208,13 @@
         <v>5</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2218,13 +2225,13 @@
         <v>5</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2238,10 +2245,10 @@
         <v>4</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2255,10 +2262,10 @@
         <v>4</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2272,10 +2279,10 @@
         <v>4</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2289,10 +2296,10 @@
         <v>4</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2306,13 +2313,14 @@
         <v>4</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/project.xlsx
+++ b/project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jirapajaisean/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D130CC5-9AFF-4749-B7E4-AF1270BF83E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B7C09B-43FA-034E-A0B0-CC298A5AAA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5720" yWindow="1840" windowWidth="28800" windowHeight="16080" xr2:uid="{C7BD4B05-5881-B742-B6C7-DB8654AD8B2F}"/>
   </bookViews>
@@ -46,9 +46,6 @@
     <t>การพักผ่อน</t>
   </si>
   <si>
-    <t>คำแนะนำการออกกำลังกายจาก AI</t>
-  </si>
-  <si>
     <t>มาก</t>
   </si>
   <si>
@@ -1154,6 +1151,9 @@
   </si>
   <si>
     <t>อ้วน 2</t>
+  </si>
+  <si>
+    <t>คำแนะนำ</t>
   </si>
 </sst>
 </file>
@@ -1548,10 +1548,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1559,16 +1559,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1576,16 +1576,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1593,16 +1593,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1610,16 +1610,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1627,16 +1627,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1644,16 +1644,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1661,16 +1661,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1678,16 +1678,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1695,16 +1695,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1712,16 +1712,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1729,16 +1729,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1746,16 +1746,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1763,16 +1763,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1780,16 +1780,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1797,16 +1797,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1814,16 +1814,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1831,16 +1831,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1848,16 +1848,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1865,16 +1865,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1882,16 +1882,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1899,16 +1899,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1916,16 +1916,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1933,16 +1933,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1950,16 +1950,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1967,16 +1967,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1984,16 +1984,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2001,16 +2001,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2018,16 +2018,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2035,16 +2035,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2052,16 +2052,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2069,16 +2069,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2086,16 +2086,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2103,16 +2103,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2120,16 +2120,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2137,16 +2137,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2154,16 +2154,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2171,16 +2171,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2188,16 +2188,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2205,16 +2205,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2222,16 +2222,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2239,16 +2239,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2256,16 +2256,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2273,16 +2273,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2290,16 +2290,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2307,16 +2307,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
